--- a/data/trans_dic/IP19C09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por otros motivos</t>
+          <t>Menores que en su última visita al dentista fue por otros motivos (tasa de respuesta: 97,59%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,7</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 6,05</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,7</t>
+          <t>0,0; 11,48</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,09</t>
+          <t>0,0; 9,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 14,68</t>
+          <t>0,0; 12,6</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,03</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,43</t>
+          <t>0,0; 3,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,33</t>
+          <t>0,66; 7,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,94</t>
+          <t>0,0; 6,09</t>
         </is>
       </c>
     </row>
@@ -787,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,41</t>
+          <t>0,55; 3,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,76; 4,03</t>
+          <t>0,62; 4,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,62</t>
+          <t>0,87; 4,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,9; 5,79</t>
+          <t>2,07; 6,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,29</t>
+          <t>0,58; 3,32</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 3,56</t>
+          <t>0,63; 3,59</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,63; 4,14</t>
+          <t>1,61; 3,92</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,98; 3,21</t>
+          <t>0,9; 3,02</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,28</t>
+          <t>1,04; 3,24</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,74</t>
+          <t>0,0; 6,65</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,69</t>
+          <t>0,0; 4,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 8,11</t>
+          <t>0,88; 8,75</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,39</t>
+          <t>0,84; 6,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,98</t>
+          <t>0,0; 6,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,62; 10,24</t>
+          <t>1,72; 10,51</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 5,09</t>
+          <t>0,85; 5,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,53</t>
+          <t>0,38; 3,75</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,11; 7,63</t>
+          <t>1,95; 7,51</t>
         </is>
       </c>
     </row>
@@ -1007,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,67</t>
+          <t>0,64; 2,85</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,72; 2,94</t>
+          <t>0,73; 3,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,2; 4,1</t>
+          <t>1,37; 4,31</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 4,98</t>
+          <t>1,83; 4,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,82; 3,52</t>
+          <t>0,84; 3,41</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,22; 4,11</t>
+          <t>1,34; 4,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,5; 3,32</t>
+          <t>1,44; 3,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,05; 2,74</t>
+          <t>1,0; 2,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,55</t>
+          <t>1,66; 3,63</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por otros motivos (tasa de respuesta: 97,59%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>609</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2329</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>564</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2820</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2479</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3999</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5413</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3014</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>593; 6301</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>0; 2903</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>3490</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>4275</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5266</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>8585</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>3528</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4228</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>12075</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>7803</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>9494</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>1260; 7752</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>1350; 9034</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2103; 10494</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>5092; 15199</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1368; 7819</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1552; 8787</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>7620; 18597</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>4072; 13669</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>5034; 15731</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1403</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>3012</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>4388</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3304</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2092</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>7400</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5033</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3876</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>744; 7396</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>614; 5077</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5497</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1479; 9008</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1265; 7439</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>620; 6165</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>3313; 12794</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>4893</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5648</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8842</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15982</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>12224</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>17458</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>2232; 10004</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>2516; 11014</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>4764; 14960</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>6609; 17076</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3037; 12290</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>4781; 15423</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>10249; 22854</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>7098; 19184</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>11667; 25541</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Estudios-trans_dic.xlsx
@@ -683,22 +683,22 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,05</t>
+          <t>0,0; 6,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 11,48</t>
+          <t>0,0; 13,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,32</t>
+          <t>0,0; 6,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 12,6</t>
+          <t>0,0; 17,16</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,17 +708,17 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,36</t>
+          <t>0,0; 3,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,66; 7,04</t>
+          <t>0,68; 7,88</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,09</t>
+          <t>0,0; 6,44</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,4</t>
+          <t>0,56; 3,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 4,15</t>
+          <t>0,72; 4,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,87; 4,35</t>
+          <t>1,04; 4,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,07; 6,19</t>
+          <t>2,06; 5,87</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 3,32</t>
+          <t>0,55; 3,38</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,63; 3,59</t>
+          <t>0,64; 3,6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,61; 3,92</t>
+          <t>1,53; 3,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,02</t>
+          <t>0,88; 2,89</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 3,24</t>
+          <t>1,13; 3,31</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,65</t>
+          <t>0,0; 6,57</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,71</t>
+          <t>0,0; 5,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 8,75</t>
+          <t>0,97; 8,54</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 6,94</t>
+          <t>0,84; 7,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,69</t>
+          <t>0,0; 5,61</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 10,51</t>
+          <t>2,22; 11,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,0</t>
+          <t>0,85; 5,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,75</t>
+          <t>0,38; 3,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,51</t>
+          <t>2,08; 7,55</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,64; 2,85</t>
+          <t>0,55; 2,66</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,18</t>
+          <t>0,77; 3,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 4,31</t>
+          <t>1,41; 4,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 4,72</t>
+          <t>1,93; 4,82</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,41</t>
+          <t>0,87; 3,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 4,33</t>
+          <t>1,32; 4,33</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,44; 3,21</t>
+          <t>1,47; 3,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,71</t>
+          <t>1,0; 2,7</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,66; 3,63</t>
+          <t>1,62; 3,58</t>
         </is>
       </c>
     </row>
@@ -1311,22 +1311,22 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2820</t>
+          <t>0; 3042</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 2479</t>
+          <t>0; 2972</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3999</t>
+          <t>0; 2999</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 5413</t>
+          <t>0; 7372</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3014</t>
+          <t>0; 3451</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>593; 6301</t>
+          <t>608; 7056</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 2903</t>
+          <t>0; 3070</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1260; 7752</t>
+          <t>1284; 8508</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1350; 9034</t>
+          <t>1558; 9674</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2103; 10494</t>
+          <t>2508; 10563</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5092; 15199</t>
+          <t>5070; 14425</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1368; 7819</t>
+          <t>1304; 7946</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1552; 8787</t>
+          <t>1576; 8810</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7620; 18597</t>
+          <t>7241; 18146</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4072; 13669</t>
+          <t>4003; 13111</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5034; 15731</t>
+          <t>5494; 16086</t>
         </is>
       </c>
     </row>
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 5033</t>
+          <t>0; 4971</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3876</t>
+          <t>0; 4113</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>744; 7396</t>
+          <t>818; 7219</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>614; 5077</t>
+          <t>612; 5710</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 5497</t>
+          <t>0; 4608</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1479; 9008</t>
+          <t>1903; 9762</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1265; 7439</t>
+          <t>1271; 7853</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>620; 6165</t>
+          <t>619; 5679</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3313; 12794</t>
+          <t>3549; 12855</t>
         </is>
       </c>
     </row>
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2232; 10004</t>
+          <t>1936; 9331</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2516; 11014</t>
+          <t>2675; 11731</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4764; 14960</t>
+          <t>4889; 14753</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6609; 17076</t>
+          <t>6994; 17441</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3037; 12290</t>
+          <t>3127; 12029</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4781; 15423</t>
+          <t>4692; 15426</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10249; 22854</t>
+          <t>10510; 23692</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7098; 19184</t>
+          <t>7083; 19105</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11667; 25541</t>
+          <t>11418; 25186</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C09-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP19C09-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1,31%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>2,61%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,09</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 14,68</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 6,53</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 13,76</t>
-        </is>
-      </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,16</t>
+          <t>0,0; 7,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 11,7</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,84</t>
+          <t>0,0; 3,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,68; 7,88</t>
+          <t>0,68; 7,33</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,44</t>
+          <t>0,0; 4,94</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,49%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>1,5%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1,73%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>1,53%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>1,96%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>2,18%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,49%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,56; 3,73</t>
+          <t>1,9; 5,79</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 4,44</t>
+          <t>0,55; 3,29</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,04; 4,38</t>
+          <t>0,61; 3,56</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,06; 5,87</t>
+          <t>0,55; 3,41</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 3,38</t>
+          <t>0,76; 4,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,64; 3,6</t>
+          <t>0,88; 4,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,83</t>
+          <t>1,63; 4,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,89</t>
+          <t>0,98; 3,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,13; 3,31</t>
+          <t>1,04; 3,28</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,62%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>5,12%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,85%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,93%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>3,56%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,62%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,57</t>
+          <t>0,0; 6,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,0</t>
+          <t>0,0; 4,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 8,54</t>
+          <t>1,62; 10,24</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 7,81</t>
+          <t>0,0; 5,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,61</t>
+          <t>0,0; 4,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,22; 11,39</t>
+          <t>0,96; 8,11</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,28</t>
+          <t>0,84; 5,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,46</t>
+          <t>0,38; 3,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 7,55</t>
+          <t>2,11; 7,63</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3,07%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2,42%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>1,39%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1,63%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>2,55%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,66</t>
+          <t>1,97; 4,98</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,39</t>
+          <t>0,82; 3,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,41; 4,25</t>
+          <t>1,22; 4,11</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,93; 4,82</t>
+          <t>0,58; 2,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,87; 3,34</t>
+          <t>0,72; 2,94</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,33</t>
+          <t>1,2; 4,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,47; 3,32</t>
+          <t>1,5; 3,32</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 2,7</t>
+          <t>1,05; 2,74</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>1,62; 3,58</t>
+          <t>1,62; 3,55</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,32 +1200,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>603</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1720</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>609</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>564</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>603</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1720</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1306,47 +1306,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0; 3040</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6308</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>0; 3042</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>0; 2972</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 2999</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 7372</t>
+          <t>0; 3304</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 2525</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3451</t>
+          <t>0; 3078</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>608; 7056</t>
+          <t>613; 6566</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 3070</t>
+          <t>0; 2353</t>
         </is>
       </c>
     </row>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>8585</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>3528</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>4228</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>3490</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4275</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>5266</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8585</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3528</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4228</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1284; 8508</t>
+          <t>4679; 14235</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1558; 9674</t>
+          <t>1305; 7749</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2508; 10563</t>
+          <t>1488; 8707</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5070; 14425</t>
+          <t>1257; 7793</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1304; 7946</t>
+          <t>1660; 8780</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1576; 8810</t>
+          <t>2114; 11136</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7241; 18146</t>
+          <t>7721; 19629</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4003; 13111</t>
+          <t>4435; 14528</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5494; 16086</t>
+          <t>5028; 15912</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1902</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1328</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>4388</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1403</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>764</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>3012</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1902</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1328</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>4388</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4971</t>
+          <t>0; 4673</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4113</t>
+          <t>0; 4091</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>818; 7219</t>
+          <t>1389; 8781</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>612; 5710</t>
+          <t>0; 4341</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4608</t>
+          <t>0; 3860</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1903; 9762</t>
+          <t>812; 6859</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1271; 7853</t>
+          <t>1252; 7567</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>619; 5679</t>
+          <t>624; 5808</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3549; 12855</t>
+          <t>3594; 12989</t>
         </is>
       </c>
     </row>
@@ -1689,27 +1689,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>8</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11090</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6576</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>8616</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>4893</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>5648</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>8842</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>11090</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6576</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>8616</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1936; 9331</t>
+          <t>7123; 18017</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2675; 11731</t>
+          <t>2946; 12686</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4889; 14753</t>
+          <t>4364; 14639</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6994; 17441</t>
+          <t>2049; 9353</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3127; 12029</t>
+          <t>2479; 10202</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4692; 15426</t>
+          <t>4151; 14237</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10510; 23692</t>
+          <t>10666; 23660</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>7083; 19105</t>
+          <t>7409; 19371</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>11418; 25186</t>
+          <t>11379; 24982</t>
         </is>
       </c>
     </row>
